--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20261016.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20261016.xlsx
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>548,404</t>
+          <t>2,279,288</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>2,279,288</t>
+          <t>548,404</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>814,897</t>
+          <t>2,017,587</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,017,587</t>
+          <t>814,897</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>146,921</t>
+          <t>101,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>101,000</t>
+          <t>146,921</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>146,386</t>
+          <t>7,222,249</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>7,222,249</t>
+          <t>146,386</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>1,728,640</t>
+          <t>764,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>764,000</t>
+          <t>1,728,640</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,137,121</t>
+          <t>1,771,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,771,000</t>
+          <t>1,137,121</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>晶豪科</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>418,000</t>
+          <t>334,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>晶豪科</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>334,000</t>
+          <t>418,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>115,000</t>
+          <t>72,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -2207,17 +2207,17 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>72,000</t>
+          <t>115,000</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
